--- a/app/templates/report/stabilised.xlsx
+++ b/app/templates/report/stabilised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43773EA-E6D9-4C86-95C3-38CF18F4376B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916C2155-97CA-4728-9C76-68F18B180934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,9 +89,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="mm/yyyy"/>
-    <numFmt numFmtId="167" formatCode="#,##0%;[Red]\-#,##0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0%;[Red]\-#,##0%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -140,7 +140,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,6 +162,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00BFB2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -229,19 +235,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -250,10 +256,14 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
       <border>
-        <top style="thin">
+        <top style="hair">
           <color auto="1"/>
         </top>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -699,12 +709,12 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="10">
+      <c r="G3" s="12">
         <f>1-SUM(D3:F3)</f>
         <v>1</v>
       </c>
@@ -712,9 +722,9 @@
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="A3:G3">
+  <conditionalFormatting sqref="A3:G99999">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$B3&lt;&gt;$B1</formula>
+      <formula>$A2&gt;$A3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/templates/report/stabilised.xlsx
+++ b/app/templates/report/stabilised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916C2155-97CA-4728-9C76-68F18B180934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D47260-265B-4459-A938-FEAFB91792B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Resource</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>Rent_short</t>
-  </si>
-  <si>
-    <t>Rent_group</t>
   </si>
   <si>
     <t>% Occup.</t>
@@ -668,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>1</v>
@@ -703,9 +700,7 @@
       <c r="F2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>

--- a/app/templates/report/stabilised.xlsx
+++ b/app/templates/report/stabilised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D47260-265B-4459-A938-FEAFB91792B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F290F7C-737F-41DE-8094-6728C9A95FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Stabilised" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stabilised!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stabilised!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -90,7 +90,7 @@
     <numFmt numFmtId="165" formatCode="mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0%;[Red]\-#,##0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -134,6 +134,11 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -169,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -219,13 +224,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -236,7 +270,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -245,6 +278,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -664,10 +706,10 @@
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -676,46 +718,46 @@
       <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="12">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="11">
         <f>1-SUM(D3:F3)</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A3:G99999">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/app/templates/report/stabilised.xlsx
+++ b/app/templates/report/stabilised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F290F7C-737F-41DE-8094-6728C9A95FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ED91D5-6B62-4B85-98B8-9D8329D50C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Resource</t>
   </si>
@@ -79,6 +79,13 @@
   </si>
   <si>
     <t>% Occup.</t>
+  </si>
+  <si>
+    <t>%
+Leakage</t>
+  </si>
+  <si>
+    <t>Leakage</t>
   </si>
 </sst>
 </file>
@@ -90,7 +97,7 @@
     <numFmt numFmtId="165" formatCode="mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0%;[Red]\-#,##0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -122,12 +129,6 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -262,7 +263,6 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -278,22 +278,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <border>
+        <top style="hair">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -693,73 +707,84 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.140625" style="1" customWidth="1"/>
-    <col min="3" max="7" width="11.85546875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="14.42578125" style="1"/>
+    <col min="3" max="8" width="11.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="14.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="11">
+      <c r="A3" s="9"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="10">
         <f>1-SUM(D3:F3)</f>
         <v>1</v>
       </c>
+      <c r="H3" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A3:G99999">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$A2&gt;$A3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H99999">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2&gt;$A3</formula>
     </cfRule>

--- a/app/templates/report/stabilised.xlsx
+++ b/app/templates/report/stabilised.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ED91D5-6B62-4B85-98B8-9D8329D50C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C475D9A1-E1E7-4506-8FE2-D928F2BBE5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,15 +69,6 @@
     <t>Occupancy</t>
   </si>
   <si>
-    <t>Rent_long</t>
-  </si>
-  <si>
-    <t>Rent_medium</t>
-  </si>
-  <si>
-    <t>Rent_short</t>
-  </si>
-  <si>
     <t>% Occup.</t>
   </si>
   <si>
@@ -86,6 +77,15 @@
   </si>
   <si>
     <t>Leakage</t>
+  </si>
+  <si>
+    <t>Pct_long</t>
+  </si>
+  <si>
+    <t>Pct_medium</t>
+  </si>
+  <si>
+    <t>Pct_short</t>
   </si>
 </sst>
 </file>
@@ -294,20 +294,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <border>
-        <top style="hair">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <strike val="0"/>
@@ -721,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>1</v>
@@ -736,7 +723,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
@@ -750,17 +737,17 @@
         <v>8</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -779,12 +766,7 @@
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="A3:G99999">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$A2&gt;$A3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H99999">
+  <conditionalFormatting sqref="A3:H99999">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2&gt;$A3</formula>
     </cfRule>
